--- a/assets/Canevas/Canevas_tests_independance.xlsx
+++ b/assets/Canevas/Canevas_tests_independance.xlsx
@@ -610,8 +610,8 @@
       <xdr:rowOff>1905</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="254685" cy="175369"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="ZoneTexte 1">
@@ -699,7 +699,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="ZoneTexte 1">
